--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487609_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487609_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.195600000000001</v>
+        <v>7.6561</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6328</v>
+        <v>8.393000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4371</v>
+        <v>-0.7369</v>
       </c>
       <c r="G2" t="n">
         <v>4.709</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1449</v>
+        <v>0.6054</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3656</v>
+        <v>0.1259</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7793</v>
+        <v>0.4795</v>
       </c>
       <c r="V2" t="n">
         <v>2.7298</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.641</v>
+        <v>0.8045</v>
       </c>
       <c r="E3" t="n">
-        <v>1.448</v>
+        <v>2.2128</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-1.4083</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4773</v>
+        <v>0.4084</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0313</v>
+        <v>-1.3651</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.446</v>
+        <v>1.7735</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2652</v>
+        <v>2.9305</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0216</v>
+        <v>0.3172</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2436</v>
+        <v>2.6133</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7425</v>
+        <v>-2.5221</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0529</v>
+        <v>-1.6824</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6896</v>
+        <v>-0.8398</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4302</v>
+        <v>-0.055</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1828</v>
+        <v>-0.4475</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2474</v>
+        <v>0.3926</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2821</v>
+        <v>-0.131</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2821</v>
+        <v>-1.025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0104</v>
+        <v>0.4699</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6913</v>
+        <v>-0.3823</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6809</v>
+        <v>0.8522</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4084</v>
+        <v>1.0648</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3651</v>
+        <v>0.1417</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7735</v>
+        <v>0.9231</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9305</v>
+        <v>2.7196</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3172</v>
+        <v>1.7631</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6133</v>
+        <v>0.9565</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5221</v>
+        <v>-1.6548</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6824</v>
+        <v>-1.6214</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8398</v>
+        <v>-0.0334</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.849</v>
+        <v>-0.2221</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9691</v>
+        <v>-0.3079</v>
       </c>
       <c r="U4" t="n">
-        <v>0.12</v>
+        <v>0.0858</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.131</v>
+        <v>-0.1788</v>
       </c>
       <c r="W4" t="n">
-        <v>0.894</v>
+        <v>-0.6597</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.025</v>
+        <v>0.4809</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.164</v>
+        <v>0.3501</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0435</v>
+        <v>1.3479</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8794999999999999</v>
+        <v>-0.9978</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0648</v>
+        <v>-0.4773</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1417</v>
+        <v>-0.0313</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9231</v>
+        <v>-0.446</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7196</v>
+        <v>1.2652</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7631</v>
+        <v>1.0216</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9565</v>
+        <v>0.2436</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6548</v>
+        <v>-1.7425</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6214</v>
+        <v>-1.0529</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0334</v>
+        <v>-0.6896</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.856</v>
+        <v>0.1394</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9691</v>
+        <v>0.0827</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1131</v>
+        <v>0.0567</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1788</v>
+        <v>-0.2821</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4809</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.313</v>
+        <v>-0.2517</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7981</v>
+        <v>2.9453</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1111</v>
+        <v>-3.197</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2188</v>
+        <v>5.859</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2472</v>
+        <v>-0.7127</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0284</v>
+        <v>6.5716</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8565</v>
+        <v>7.9369</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5901</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2664</v>
+        <v>7.1501</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6377</v>
+        <v>-2.0779</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3429</v>
+        <v>-1.4995</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2948</v>
+        <v>-0.5784</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7761</v>
+        <v>-3.2985</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>-5.0448</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>2.153</v>
+        <v>-0.1856</v>
       </c>
       <c r="T6" t="n">
-        <v>1.882</v>
+        <v>-0.2288</v>
       </c>
       <c r="U6" t="n">
-        <v>0.271</v>
+        <v>0.0432</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.9086</v>
+        <v>-2.6265</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X6" t="n">
         <v>-2.9086</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>P. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4189</v>
+        <v>-1.6679</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0234</v>
+        <v>-1.9779</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.4423</v>
+        <v>0.31</v>
       </c>
       <c r="G7" t="n">
-        <v>5.859</v>
+        <v>-0.3795</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7127</v>
+        <v>-1.1625</v>
       </c>
       <c r="I7" t="n">
-        <v>6.5716</v>
+        <v>0.783</v>
       </c>
       <c r="J7" t="n">
-        <v>7.9369</v>
+        <v>0.044</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7868000000000001</v>
+        <v>-0.6055</v>
       </c>
       <c r="L7" t="n">
-        <v>7.1501</v>
+        <v>0.6495</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0779</v>
+        <v>-0.4235</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4995</v>
+        <v>-0.5569</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5784</v>
+        <v>0.1335</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.2985</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0448</v>
+        <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3528</v>
+        <v>-0.1242</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1508</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2021</v>
+        <v>-0.0426</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.6265</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.9086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5832</v>
+        <v>-2.096</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.131</v>
+        <v>-1.671</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4522</v>
+        <v>-0.4249</v>
       </c>
       <c r="G8" t="n">
         <v>0.1079</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4432</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6684</v>
+        <v>0.1284</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2252</v>
+        <v>-0.1979</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ RODRIGUEZ</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8225</v>
+        <v>-2.7987</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.078</v>
+        <v>-0.2549</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2555</v>
+        <v>-2.5437</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3795</v>
+        <v>-0.5349</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1625</v>
+        <v>-2.1816</v>
       </c>
       <c r="I9" t="n">
-        <v>0.783</v>
+        <v>1.6467</v>
       </c>
       <c r="J9" t="n">
-        <v>0.044</v>
+        <v>1.9263</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6055</v>
+        <v>-0.5602</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6495</v>
+        <v>2.4865</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4235</v>
+        <v>-2.4612</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5569</v>
+        <v>-1.6214</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1335</v>
+        <v>-0.8398</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1642</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9403</v>
+        <v>-2.1344</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2788</v>
+        <v>-0.7551</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1817</v>
+        <v>-0.3289</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.4262</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.1206</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4027</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.669</v>
+        <v>-2.9843</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0162</v>
+        <v>0.3177</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6528</v>
+        <v>-3.3019</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5349</v>
+        <v>0.2188</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1816</v>
+        <v>0.2472</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6467</v>
+        <v>-0.0284</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9263</v>
+        <v>1.8565</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5602</v>
+        <v>1.5901</v>
       </c>
       <c r="L10" t="n">
-        <v>2.4865</v>
+        <v>0.2664</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4612</v>
+        <v>-1.6377</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6214</v>
+        <v>-1.3429</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8398</v>
+        <v>-0.2948</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3881</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1344</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6254</v>
+        <v>0.4817</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0902</v>
+        <v>0.4015</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5352</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1206</v>
+        <v>-2.9086</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4027</v>
+        <v>-2.9086</v>
       </c>
     </row>
     <row r="11">
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1236</v>
+        <v>-0.5180000000000007</v>
       </c>
       <c r="E11" t="n">
-        <v>10.3249</v>
+        <v>10.9306</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.4484</v>
+        <v>-11.4483</v>
       </c>
       <c r="G11" t="n">
         <v>10.9762</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.541500000000001</v>
+        <v>-6.5415</v>
       </c>
       <c r="I11" t="n">
         <v>17.5176</v>
@@ -1303,7 +1303,7 @@
         <v>-2.92</v>
       </c>
       <c r="P11" t="n">
-        <v>-6.791099999999999</v>
+        <v>-6.7911</v>
       </c>
       <c r="Q11" t="n">
         <v>-19.4033</v>
@@ -1312,19 +1312,19 @@
         <v>12.6121</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7907000000000001</v>
+        <v>-0.1849999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2621</v>
+        <v>-0.6562000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4712</v>
+        <v>0.4713</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.517799999999999</v>
+        <v>-4.5178</v>
       </c>
       <c r="W11" t="n">
-        <v>4.752199999999999</v>
+        <v>4.7522</v>
       </c>
       <c r="X11" t="n">
         <v>-9.27</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.148</v>
+        <v>2.9715</v>
       </c>
       <c r="E12" t="n">
-        <v>6.263</v>
+        <v>5.1695</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.115</v>
+        <v>-2.1979</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8894</v>
+        <v>-2.2323</v>
       </c>
       <c r="H12" t="n">
-        <v>6.1477</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.2583</v>
+        <v>-3.127</v>
       </c>
       <c r="J12" t="n">
-        <v>7.386</v>
+        <v>2.1077</v>
       </c>
       <c r="K12" t="n">
-        <v>7.1018</v>
+        <v>1.4253</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2842</v>
+        <v>0.6824</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.4966</v>
+        <v>-4.3401</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.5306</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.5425</v>
+        <v>-3.8095</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R12" t="n">
-        <v>3.2985</v>
+        <v>2.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0258</v>
+        <v>-0.1663</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1069</v>
+        <v>-0.2919</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9188</v>
+        <v>0.1256</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9314</v>
+        <v>3.6238</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.0955</v>
+        <v>4.5179</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8358</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6167</v>
+        <v>2.7654</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8692</v>
+        <v>5.262</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2525</v>
+        <v>-2.4966</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2323</v>
+        <v>2.8894</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8947000000000001</v>
+        <v>6.1477</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.127</v>
+        <v>-3.2583</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1077</v>
+        <v>7.386</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4253</v>
+        <v>7.1018</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6824</v>
+        <v>0.2842</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.3401</v>
+        <v>-4.4966</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5306</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.8095</v>
+        <v>-3.5425</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R13" t="n">
-        <v>2.9105</v>
+        <v>3.2985</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5211</v>
+        <v>0.6432</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.1059</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0711</v>
+        <v>0.5373</v>
       </c>
       <c r="V13" t="n">
-        <v>3.6238</v>
+        <v>-1.9314</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5179</v>
+        <v>-0.0955</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.894</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9398</v>
+        <v>2.7039</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5864</v>
+        <v>3.187</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6466</v>
+        <v>-0.4831</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7196</v>
@@ -1546,13 +1546,13 @@
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0182</v>
+        <v>-0.254</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9567</v>
+        <v>-0.3561</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0614</v>
+        <v>0.1021</v>
       </c>
       <c r="V14" t="n">
         <v>1.9314</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2969</v>
+        <v>1.7422</v>
       </c>
       <c r="E15" t="n">
-        <v>0.804</v>
+        <v>4.27</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4929</v>
+        <v>-2.5278</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7946</v>
+        <v>-1.9976</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1305</v>
+        <v>-0.5289</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3359</v>
+        <v>-1.4687</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0471</v>
+        <v>3.2994</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9659</v>
+        <v>0.2801</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08119999999999999</v>
+        <v>3.0193</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2525</v>
+        <v>-5.297</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8354</v>
+        <v>-0.8091</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4171</v>
+        <v>-4.4879</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5523</v>
+        <v>2.7164</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1097</v>
+        <v>-0.2602</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3028</v>
+        <v>-0.313</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1932</v>
+        <v>0.0527</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2873</v>
+        <v>1.4881</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8696</v>
+        <v>1.1043</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.5823</v>
+        <v>0.3839</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9976</v>
+        <v>1.7946</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5289</v>
+        <v>2.1305</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4687</v>
+        <v>-0.3359</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2994</v>
+        <v>3.0471</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2801</v>
+        <v>2.9659</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0193</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.297</v>
+        <v>-1.2525</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8091</v>
+        <v>-0.8354</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.4879</v>
+        <v>-0.4171</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.3881</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.5523</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.1642</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.7164</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.7151</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7134</v>
+        <v>-0.0025</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0018</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5359</v>
+        <v>0.2173</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0593</v>
+        <v>-0.4597</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5952</v>
+        <v>0.677</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8286</v>
@@ -1780,13 +1780,13 @@
         <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2003</v>
+        <v>-0.1183</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5462</v>
+        <v>0.1458</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3459</v>
+        <v>-0.2641</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4451</v>
+        <v>-1.3088</v>
       </c>
       <c r="E18" t="n">
         <v>-2.1185</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6733</v>
+        <v>0.8096</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2156</v>
@@ -1858,13 +1858,13 @@
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3824</v>
+        <v>0.5187</v>
       </c>
       <c r="T18" t="n">
         <v>0.4251</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0426</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BUTUNOI</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5822</v>
+        <v>-1.6458</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2822</v>
+        <v>-0.6958</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3</v>
+        <v>-0.95</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3854</v>
+        <v>-1.3557</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0206</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.406</v>
+        <v>-0.4115</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0206</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0206</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.406</v>
+        <v>-0.7625</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.351</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.406</v>
+        <v>-0.4115</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6673</v>
+        <v>0.1576</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6673</v>
+        <v>-0.1026</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2602</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>D. BUTUNOI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6825</v>
+        <v>-1.9826</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.896</v>
+        <v>-0.6826</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7865</v>
+        <v>-1.3</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3557</v>
+        <v>-0.3854</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9441000000000001</v>
+        <v>0.0206</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4115</v>
+        <v>-0.406</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0206</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0206</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7625</v>
+        <v>-0.406</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.351</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4115</v>
+        <v>-0.406</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1209</v>
+        <v>0.2669</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3028</v>
+        <v>0.2669</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4237</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2239</v>
+        <v>-0.894</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4693</v>
+        <v>-2.9124</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8324</v>
+        <v>-2.2549</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6369</v>
+        <v>-0.6575</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0164</v>
+        <v>-1.9088</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4317</v>
+        <v>1.1303</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.5847</v>
+        <v>-3.0392</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6021</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5108</v>
+        <v>1.7713</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09130000000000001</v>
+        <v>-1.1317</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.6185</v>
+        <v>-2.5485</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9425</v>
+        <v>-0.641</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.676</v>
+        <v>-1.9075</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7761</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1344</v>
+        <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9105</v>
+        <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2068</v>
+        <v>0.1607</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1357</v>
+        <v>0.016</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0711</v>
+        <v>0.1447</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5219</v>
+        <v>-2.9153</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7554</v>
+        <v>-1.3329</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7665</v>
+        <v>-1.5824</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9088</v>
+        <v>-4.0164</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1303</v>
+        <v>-0.4317</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0392</v>
+        <v>-3.5847</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6021</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7713</v>
+        <v>0.5108</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1317</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5485</v>
+        <v>-4.6185</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.641</v>
+        <v>-0.9425</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9075</v>
+        <v>-3.676</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9105</v>
+        <v>-2.1344</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7463</v>
+        <v>2.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4489</v>
+        <v>-0.2392</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4845</v>
+        <v>-0.3648</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0357</v>
+        <v>0.1256</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1236</v>
+        <v>1.1235</v>
       </c>
       <c r="E23" t="n">
         <v>11.4484</v>
       </c>
       <c r="F23" t="n">
-        <v>-10.3249</v>
+        <v>-10.3248</v>
       </c>
       <c r="G23" t="n">
         <v>-10.976</v>
       </c>
       <c r="H23" t="n">
-        <v>6.541600000000001</v>
+        <v>6.5416</v>
       </c>
       <c r="I23" t="n">
         <v>-17.5176</v>
@@ -2239,7 +2239,7 @@
         <v>-20.4377</v>
       </c>
       <c r="P23" t="n">
-        <v>6.791099999999999</v>
+        <v>6.7911</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.6122</v>
@@ -2248,7 +2248,7 @@
         <v>19.4032</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7905</v>
+        <v>0.7907000000000001</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4712</v>
@@ -2257,7 +2257,7 @@
         <v>1.2619</v>
       </c>
       <c r="V23" t="n">
-        <v>4.5178</v>
+        <v>4.517799999999999</v>
       </c>
       <c r="W23" t="n">
         <v>9.270099999999999</v>
